--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.8891549801431</v>
+        <v>6.156987684273255</v>
       </c>
       <c r="D2" t="n">
-        <v>41.46505542350796</v>
+        <v>6.738071506320044</v>
       </c>
       <c r="E2" t="n">
-        <v>12.36840964037563</v>
+        <v>2.00986656656104</v>
       </c>
       <c r="F2" t="n">
-        <v>12.9780496022863</v>
+        <v>2.108933060371524</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.96239032449916</v>
+        <v>7.143888427731114</v>
       </c>
       <c r="D3" t="n">
-        <v>47.9640271055072</v>
+        <v>7.79415440464492</v>
       </c>
       <c r="E3" t="n">
-        <v>12.36840964037563</v>
+        <v>2.00986656656104</v>
       </c>
       <c r="F3" t="n">
-        <v>12.9780496022863</v>
+        <v>2.108933060371524</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>4.931282855207694</v>
+        <v>0.8013334639712504</v>
       </c>
       <c r="D4" t="n">
-        <v>61.16144081233233</v>
+        <v>9.938734132004004</v>
       </c>
       <c r="E4" t="n">
-        <v>12.36840964037563</v>
+        <v>2.00986656656104</v>
       </c>
       <c r="F4" t="n">
-        <v>12.9780496022863</v>
+        <v>2.108933060371524</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.57355312022687</v>
+        <v>3.993202382036867</v>
       </c>
       <c r="D5" t="n">
-        <v>21.82843797566808</v>
+        <v>3.547121171046063</v>
       </c>
       <c r="E5" t="n">
-        <v>12.36840964037563</v>
+        <v>2.00986656656104</v>
       </c>
       <c r="F5" t="n">
-        <v>12.9780496022863</v>
+        <v>2.108933060371524</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.74112885855023</v>
+        <v>2.395433439514413</v>
       </c>
       <c r="D6" t="n">
-        <v>55.81872028402186</v>
+        <v>9.070542046153554</v>
       </c>
       <c r="E6" t="n">
-        <v>12.36840964037563</v>
+        <v>2.00986656656104</v>
       </c>
       <c r="F6" t="n">
-        <v>12.9780496022863</v>
+        <v>2.108933060371524</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.24686959014105</v>
+        <v>5.890116308397921</v>
       </c>
       <c r="D7" t="n">
-        <v>36.70794909205483</v>
+        <v>5.96504172745891</v>
       </c>
       <c r="E7" t="n">
-        <v>12.36840964037563</v>
+        <v>2.00986656656104</v>
       </c>
       <c r="F7" t="n">
-        <v>12.9780496022863</v>
+        <v>2.108933060371524</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.10676877297979</v>
+        <v>4.567349925609216</v>
       </c>
       <c r="D8" t="n">
-        <v>28.51558570531736</v>
+        <v>4.633782677114072</v>
       </c>
       <c r="E8" t="n">
-        <v>12.36840964037563</v>
+        <v>2.00986656656104</v>
       </c>
       <c r="F8" t="n">
-        <v>12.9780496022863</v>
+        <v>2.108933060371524</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.20951744279908</v>
+        <v>7.02154658445485</v>
       </c>
       <c r="D9" t="n">
-        <v>52.59371521629886</v>
+        <v>8.546478722648565</v>
       </c>
       <c r="E9" t="n">
-        <v>12.36840964037563</v>
+        <v>2.00986656656104</v>
       </c>
       <c r="F9" t="n">
-        <v>12.9780496022863</v>
+        <v>2.108933060371524</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>41.60178462221418</v>
+        <v>6.760290001109804</v>
       </c>
       <c r="D10" t="n">
-        <v>48.13975427126088</v>
+        <v>7.822710069079894</v>
       </c>
       <c r="E10" t="n">
-        <v>12.36840964037563</v>
+        <v>2.00986656656104</v>
       </c>
       <c r="F10" t="n">
-        <v>12.9780496022863</v>
+        <v>2.108933060371524</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.50698066088976</v>
+        <v>3.982384357394586</v>
       </c>
       <c r="D11" t="n">
-        <v>24.00001485422325</v>
+        <v>3.900002413811278</v>
       </c>
       <c r="E11" t="n">
-        <v>12.36840964037563</v>
+        <v>2.00986656656104</v>
       </c>
       <c r="F11" t="n">
-        <v>12.9780496022863</v>
+        <v>2.108933060371524</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
